--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1482,7 +1482,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>45</v>
@@ -1602,7 +1602,7 @@
         <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>67</v>
@@ -1713,7 +1713,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="1:8">
+    <row r="19" ht="28" customHeight="1" spans="2:8">
       <c r="B19" s="2">
         <v>15</v>
       </c>

--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1713,7 +1713,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="2:8">
+    <row r="19" ht="28" customHeight="1" spans="1:8">
       <c r="B19" s="2">
         <v>15</v>
       </c>

--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -172,9 +172,6 @@
     <t>开局获得中等数量特殊子弹，提升前期爆发</t>
   </si>
   <si>
-    <t>HuntingConfig.Bean.LuckyBuffParamStartSpecialBullet,2</t>
-  </si>
-  <si>
     <t>中档：开局获得2发特殊子弹</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>开局获得大量特殊子弹，显著提升前期爆发</t>
   </si>
   <si>
-    <t>HuntingConfig.Bean.LuckyBuffParamStartSpecialBullet,3</t>
-  </si>
-  <si>
     <t>强档：开局获得3发特殊子弹</t>
   </si>
   <si>
@@ -241,7 +235,7 @@
     <t>HuntingConfig.Bean.LuckyBuffParamDamageBoost,1.20</t>
   </si>
   <si>
-    <t>弱档：伤害 ×1.2</t>
+    <t>弱档：伤害 ×4</t>
   </si>
   <si>
     <t>伤害提升·2级</t>
@@ -253,7 +247,7 @@
     <t>HuntingConfig.Bean.LuckyBuffParamDamageBoost,1.50</t>
   </si>
   <si>
-    <t>中档：伤害 ×1.5</t>
+    <t>中档：伤害 ×8</t>
   </si>
   <si>
     <t>伤害提升·3级</t>
@@ -265,7 +259,7 @@
     <t>HuntingConfig.Bean.LuckyBuffParamDamageBoost,2.00</t>
   </si>
   <si>
-    <t>强档：伤害 ×2.0</t>
+    <t>强档：伤害 ×16</t>
   </si>
   <si>
     <t>HighTierSpawn</t>
@@ -1491,10 +1485,10 @@
         <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
@@ -1509,16 +1503,16 @@
         <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
@@ -1527,22 +1521,22 @@
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
@@ -1551,22 +1545,22 @@
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
@@ -1575,22 +1569,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
@@ -1599,22 +1593,22 @@
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
@@ -1623,22 +1617,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:8">
@@ -1647,22 +1641,22 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:8">
@@ -1671,22 +1665,22 @@
         <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:8">
@@ -1695,45 +1689,45 @@
         <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:8">
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="2:8">
       <c r="B19" s="2">
         <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1707,7 +1707,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="2:8">
+    <row r="19" ht="28" customHeight="1" spans="1:8">
       <c r="B19" s="2">
         <v>15</v>
       </c>

--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23925" windowHeight="12030"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Datas/LuckyBuff.xlsx
+++ b/Datas/LuckyBuff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23925" windowHeight="12030"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -149,39 +149,6 @@
   </si>
   <si>
     <t>强档：30% 概率，额外 ×3.0</t>
-  </si>
-  <si>
-    <t>StartSpecialBullet</t>
-  </si>
-  <si>
-    <t>开局特殊子弹·1级</t>
-  </si>
-  <si>
-    <t>开局获得少量特殊子弹，用于强化前期输出</t>
-  </si>
-  <si>
-    <t>HuntingConfig.Bean.LuckyBuffParamStartSpecialBullet,1</t>
-  </si>
-  <si>
-    <t>弱档：开局获得1发特殊子弹</t>
-  </si>
-  <si>
-    <t>开局特殊子弹·2级</t>
-  </si>
-  <si>
-    <t>开局获得中等数量特殊子弹，提升前期爆发</t>
-  </si>
-  <si>
-    <t>中档：开局获得2发特殊子弹</t>
-  </si>
-  <si>
-    <t>开局特殊子弹·3级</t>
-  </si>
-  <si>
-    <t>开局获得大量特殊子弹，显著提升前期爆发</t>
-  </si>
-  <si>
-    <t>强档：开局获得3发特殊子弹</t>
   </si>
   <si>
     <t>StartEnergy</t>
@@ -1256,7 +1223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
@@ -1446,7 +1413,7 @@
     <row r="8" ht="28" customHeight="1" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>40</v>
@@ -1470,7 +1437,7 @@
     <row r="9" ht="28" customHeight="1" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>40</v>
@@ -1485,16 +1452,16 @@
         <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:8">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>40</v>
@@ -1503,231 +1470,159 @@
         <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:8">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:8">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:8">
       <c r="A15" s="2"/>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="1:8">
-      <c r="A16" s="2"/>
+    <row r="16" ht="28" customHeight="1" spans="2:8">
       <c r="B16" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:8">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:8">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:8">
-      <c r="B19" s="2">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
